--- a/assets/Luz Triunfal.xlsx
+++ b/assets/Luz Triunfal.xlsx
@@ -801,7 +801,7 @@
         <v>Common</v>
       </c>
       <c r="F12" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G12" t="str">
         <v>POKEMON</v>
@@ -836,7 +836,7 @@
         <v>Uncommon</v>
       </c>
       <c r="F13" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G13" t="str">
         <v>POKEMON</v>
@@ -1501,7 +1501,7 @@
         <v>Common</v>
       </c>
       <c r="F32" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G32" t="str">
         <v>POKEMON</v>
@@ -1536,7 +1536,7 @@
         <v>Common</v>
       </c>
       <c r="F33" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G33" t="str">
         <v>POKEMON</v>
@@ -1571,7 +1571,7 @@
         <v>Uncommon</v>
       </c>
       <c r="F34" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G34" t="str">
         <v>POKEMON</v>
@@ -1956,7 +1956,7 @@
         <v>Common</v>
       </c>
       <c r="F45" t="str">
-        <v>Volador</v>
+        <v>Incoloro</v>
       </c>
       <c r="G45" t="str">
         <v>POKEMON</v>
@@ -1991,7 +1991,7 @@
         <v>Common</v>
       </c>
       <c r="F46" t="str">
-        <v>Volador</v>
+        <v>Incoloro</v>
       </c>
       <c r="G46" t="str">
         <v>POKEMON</v>
@@ -2201,7 +2201,7 @@
         <v>Common</v>
       </c>
       <c r="F52" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G52" t="str">
         <v>POKEMON</v>
@@ -2236,7 +2236,7 @@
         <v>Uncommon</v>
       </c>
       <c r="F53" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G53" t="str">
         <v>POKEMON</v>
@@ -2271,7 +2271,7 @@
         <v>Common</v>
       </c>
       <c r="F54" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G54" t="str">
         <v>POKEMON</v>
@@ -2306,7 +2306,7 @@
         <v>Double Rare</v>
       </c>
       <c r="F55" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G55" t="str">
         <v>POKEMON</v>
@@ -2621,7 +2621,7 @@
         <v>Common</v>
       </c>
       <c r="F64" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G64" t="str">
         <v>POKEMON</v>
@@ -3461,7 +3461,7 @@
         <v>1 Star Rare</v>
       </c>
       <c r="F88" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G88" t="str">
         <v>POKEMON</v>
@@ -3496,7 +3496,7 @@
         <v>1 Star Rare</v>
       </c>
       <c r="F89" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G89" t="str">
         <v>POKEMON</v>
@@ -3531,7 +3531,7 @@
         <v>2 Star Rare</v>
       </c>
       <c r="F90" t="str">
-        <v>Oscuridad</v>
+        <v>Oscura</v>
       </c>
       <c r="G90" t="str">
         <v>POKEMON</v>
